--- a/web/public/forms/geomcheuk-pojang.xlsx
+++ b/web/public/forms/geomcheuk-pojang.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="포장공 검측 체크리스트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'포장공 검측 체크리스트'!$A$1:$X$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'포장공 검측 체크리스트'!$A$1:$X$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,37 +36,58 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +96,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,23 +125,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -114,35 +150,59 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X50"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -538,15 +598,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -570,7 +630,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -600,7 +660,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -630,7 +690,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -660,7 +720,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -690,7 +750,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -711,7 +771,7 @@
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>▣ 보조기층,기층</t>
         </is>
@@ -719,13 +779,13 @@
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
         </is>
@@ -739,7 +799,7 @@
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="n"/>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>검사기준</t>
         </is>
@@ -747,19 +807,19 @@
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>합격</t>
         </is>
       </c>
       <c r="R13" s="5" t="n"/>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S13" s="9" t="inlineStr">
         <is>
           <t>불합격</t>
         </is>
       </c>
       <c r="T13" s="5" t="n"/>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="U13" s="9" t="inlineStr">
         <is>
           <t>조치사항</t>
         </is>
@@ -768,14 +828,14 @@
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
-    <row r="14" ht="43.5" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>재료의 입도분포 및 유해물 포함여부?</t>
         </is>
@@ -789,27 +849,27 @@
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="n"/>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="10" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="Q14" s="10" t="n"/>
       <c r="R14" s="5" t="n"/>
-      <c r="S14" s="9" t="inlineStr"/>
+      <c r="S14" s="10" t="n"/>
       <c r="T14" s="5" t="n"/>
-      <c r="U14" s="9" t="inlineStr"/>
+      <c r="U14" s="10" t="n"/>
       <c r="V14" s="5" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>다짐층의 두께(20cm) 및 전압밀도(95%) 적정 여부?</t>
         </is>
@@ -823,27 +883,27 @@
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="n"/>
-      <c r="M15" s="9" t="inlineStr"/>
+      <c r="M15" s="10" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="9" t="inlineStr"/>
+      <c r="Q15" s="10" t="n"/>
       <c r="R15" s="5" t="n"/>
-      <c r="S15" s="9" t="inlineStr"/>
+      <c r="S15" s="10" t="n"/>
       <c r="T15" s="5" t="n"/>
-      <c r="U15" s="9" t="inlineStr"/>
+      <c r="U15" s="10" t="n"/>
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>포설시 최적함수비 유지 및 입도분리 방지대책 강구 여부?</t>
         </is>
@@ -857,27 +917,27 @@
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="n"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="10" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="Q16" s="10" t="n"/>
       <c r="R16" s="5" t="n"/>
-      <c r="S16" s="9" t="inlineStr"/>
+      <c r="S16" s="10" t="n"/>
       <c r="T16" s="5" t="n"/>
-      <c r="U16" s="9" t="inlineStr"/>
+      <c r="U16" s="10" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
-    <row r="17" ht="43.5" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>구조물 주위의 다짐 및 보호상태 여부?</t>
         </is>
@@ -891,27 +951,27 @@
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="10" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="Q17" s="10" t="n"/>
       <c r="R17" s="5" t="n"/>
-      <c r="S17" s="9" t="inlineStr"/>
+      <c r="S17" s="10" t="n"/>
       <c r="T17" s="5" t="n"/>
-      <c r="U17" s="9" t="inlineStr"/>
+      <c r="U17" s="10" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
-    <row r="18" ht="43.5" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>사면의 구배 및 배수로 상태의 적정여부?</t>
         </is>
@@ -925,27 +985,27 @@
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
-      <c r="M18" s="9" t="inlineStr"/>
+      <c r="M18" s="10" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="Q18" s="10" t="n"/>
       <c r="R18" s="5" t="n"/>
-      <c r="S18" s="9" t="inlineStr"/>
+      <c r="S18" s="10" t="n"/>
       <c r="T18" s="5" t="n"/>
-      <c r="U18" s="9" t="inlineStr"/>
+      <c r="U18" s="10" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
-    <row r="19" ht="43.5" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>규정된 성형,단면,표고,구배의 적정여부?</t>
         </is>
@@ -959,27 +1019,27 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
-      <c r="M19" s="9" t="inlineStr"/>
+      <c r="M19" s="10" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="Q19" s="10" t="n"/>
       <c r="R19" s="5" t="n"/>
-      <c r="S19" s="9" t="inlineStr"/>
+      <c r="S19" s="10" t="n"/>
       <c r="T19" s="5" t="n"/>
-      <c r="U19" s="9" t="inlineStr"/>
+      <c r="U19" s="10" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>보조기층 시공전 노면상의 스폰지,먼지, 점토, 기타 불순물을 깨끗이 정리여부?</t>
         </is>
@@ -993,88 +1053,71 @@
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
-      <c r="M20" s="9" t="inlineStr"/>
+      <c r="M20" s="10" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="9" t="inlineStr"/>
+      <c r="Q20" s="10" t="n"/>
       <c r="R20" s="5" t="n"/>
-      <c r="S20" s="9" t="inlineStr"/>
+      <c r="S20" s="10" t="n"/>
       <c r="T20" s="5" t="n"/>
-      <c r="U20" s="9" t="inlineStr"/>
+      <c r="U20" s="10" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="13">
+        <f>IF(COUNTA(Q14:Q20,S14:S20)=0,"","합격 "&amp;COUNTA(Q14:Q20)&amp;" · 불합격 "&amp;COUNTA(S14:S20))</f>
+        <v/>
+      </c>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>▣ 보조기층, 기층</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="6" customHeight="1"/>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="8" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="43.5" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>각종 관리시험의 이행 및 결과의 보존 여부?</t>
         </is>
       </c>
       <c r="D25" s="5" t="n"/>
@@ -1086,29 +1129,45 @@
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
-      <c r="M25" s="9" t="inlineStr"/>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
       <c r="R25" s="5" t="n"/>
-      <c r="S25" s="9" t="inlineStr"/>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
       <c r="T25" s="5" t="n"/>
-      <c r="U25" s="9" t="inlineStr"/>
+      <c r="U25" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
-    <row r="26" ht="43.5" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>두께는 시방서에 규정된 허용 범위내에 드는지 여부?</t>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>각종 관리시험의 이행 및 결과의 보존 여부?</t>
         </is>
       </c>
       <c r="D26" s="5" t="n"/>
@@ -1120,122 +1179,105 @@
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="n"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="10" t="n"/>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="Q26" s="10" t="n"/>
       <c r="R26" s="5" t="n"/>
-      <c r="S26" s="9" t="inlineStr"/>
+      <c r="S26" s="10" t="n"/>
       <c r="T26" s="5" t="n"/>
-      <c r="U26" s="9" t="inlineStr"/>
+      <c r="U26" s="10" t="n"/>
       <c r="V26" s="5" t="n"/>
       <c r="W26" s="5" t="n"/>
       <c r="X26" s="5" t="n"/>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>두께는 시방서에 규정된 허용 범위내에 드는지 여부?</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="13">
+        <f>IF(COUNTA(Q26:Q27,S26:S27)=0,"","합격 "&amp;COUNTA(Q26:Q27)&amp;" · 불합격 "&amp;COUNTA(S26:S27))</f>
+        <v/>
+      </c>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>▣ 아스팔트 포장</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="8" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="8" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>기층표면 청소상태의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="9" t="inlineStr"/>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="9" t="inlineStr"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="9" t="inlineStr"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="43.5" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>프라임 텍코트용 역청재의 사용량,살포온도,양생기간의 적정여부?</t>
         </is>
       </c>
       <c r="D32" s="5" t="n"/>
@@ -1247,29 +1289,45 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="5" t="n"/>
-      <c r="M32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="9" t="inlineStr"/>
+      <c r="Q32" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
       <c r="R32" s="5" t="n"/>
-      <c r="S32" s="9" t="inlineStr"/>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
       <c r="T32" s="5" t="n"/>
-      <c r="U32" s="9" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
       <c r="V32" s="5" t="n"/>
       <c r="W32" s="5" t="n"/>
       <c r="X32" s="5" t="n"/>
     </row>
-    <row r="33" ht="43.5" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>골재 가열온도,혼합물, 생산 및 현장도착시의 온도관리?</t>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>기층표면 청소상태의 적정여부?</t>
         </is>
       </c>
       <c r="D33" s="5" t="n"/>
@@ -1281,29 +1339,29 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="5" t="n"/>
       <c r="L33" s="5" t="n"/>
-      <c r="M33" s="9" t="inlineStr"/>
+      <c r="M33" s="10" t="n"/>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="9" t="inlineStr"/>
+      <c r="Q33" s="10" t="n"/>
       <c r="R33" s="5" t="n"/>
-      <c r="S33" s="9" t="inlineStr"/>
+      <c r="S33" s="10" t="n"/>
       <c r="T33" s="5" t="n"/>
-      <c r="U33" s="9" t="inlineStr"/>
+      <c r="U33" s="10" t="n"/>
       <c r="V33" s="5" t="n"/>
       <c r="W33" s="5" t="n"/>
       <c r="X33" s="5" t="n"/>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>포설중 혼합물의 재료분리 여부?</t>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>프라임 텍코트용 역청재의 사용량,살포온도,양생기간의 적정여부?</t>
         </is>
       </c>
       <c r="D34" s="5" t="n"/>
@@ -1315,29 +1373,29 @@
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="5" t="n"/>
-      <c r="M34" s="9" t="inlineStr"/>
+      <c r="M34" s="10" t="n"/>
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="9" t="inlineStr"/>
+      <c r="Q34" s="10" t="n"/>
       <c r="R34" s="5" t="n"/>
-      <c r="S34" s="9" t="inlineStr"/>
+      <c r="S34" s="10" t="n"/>
       <c r="T34" s="5" t="n"/>
-      <c r="U34" s="9" t="inlineStr"/>
+      <c r="U34" s="10" t="n"/>
       <c r="V34" s="5" t="n"/>
       <c r="W34" s="5" t="n"/>
       <c r="X34" s="5" t="n"/>
     </row>
-    <row r="35" ht="43.5" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>포장 장비의 조합, 전압순서 및 회수등의 시공계획 수립여부?</t>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>골재 가열온도,혼합물, 생산 및 현장도착시의 온도관리?</t>
         </is>
       </c>
       <c r="D35" s="5" t="n"/>
@@ -1349,29 +1407,29 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
-      <c r="M35" s="9" t="inlineStr"/>
+      <c r="M35" s="10" t="n"/>
       <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="9" t="inlineStr"/>
+      <c r="Q35" s="10" t="n"/>
       <c r="R35" s="5" t="n"/>
-      <c r="S35" s="9" t="inlineStr"/>
+      <c r="S35" s="10" t="n"/>
       <c r="T35" s="5" t="n"/>
-      <c r="U35" s="9" t="inlineStr"/>
+      <c r="U35" s="10" t="n"/>
       <c r="V35" s="5" t="n"/>
       <c r="W35" s="5" t="n"/>
       <c r="X35" s="5" t="n"/>
     </row>
-    <row r="36" ht="43.5" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="B36" s="5" t="n"/>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>완성된 포장의 두께 및 평탄성과 유지관리 상태의 적정여부?</t>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>포설중 혼합물의 재료분리 여부?</t>
         </is>
       </c>
       <c r="D36" s="5" t="n"/>
@@ -1383,29 +1441,29 @@
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
-      <c r="M36" s="9" t="inlineStr"/>
+      <c r="M36" s="10" t="n"/>
       <c r="N36" s="5" t="n"/>
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="9" t="inlineStr"/>
+      <c r="Q36" s="10" t="n"/>
       <c r="R36" s="5" t="n"/>
-      <c r="S36" s="9" t="inlineStr"/>
+      <c r="S36" s="10" t="n"/>
       <c r="T36" s="5" t="n"/>
-      <c r="U36" s="9" t="inlineStr"/>
+      <c r="U36" s="10" t="n"/>
       <c r="V36" s="5" t="n"/>
       <c r="W36" s="5" t="n"/>
       <c r="X36" s="5" t="n"/>
     </row>
-    <row r="37" ht="43.5" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="B37" s="5" t="n"/>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>각종 시험관리의 이행 및 결과 보존여부?</t>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>포장 장비의 조합, 전압순서 및 회수등의 시공계획 수립여부?</t>
         </is>
       </c>
       <c r="D37" s="5" t="n"/>
@@ -1417,29 +1475,29 @@
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="5" t="n"/>
       <c r="L37" s="5" t="n"/>
-      <c r="M37" s="9" t="inlineStr"/>
+      <c r="M37" s="10" t="n"/>
       <c r="N37" s="5" t="n"/>
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="9" t="inlineStr"/>
+      <c r="Q37" s="10" t="n"/>
       <c r="R37" s="5" t="n"/>
-      <c r="S37" s="9" t="inlineStr"/>
+      <c r="S37" s="10" t="n"/>
       <c r="T37" s="5" t="n"/>
-      <c r="U37" s="9" t="inlineStr"/>
+      <c r="U37" s="10" t="n"/>
       <c r="V37" s="5" t="n"/>
       <c r="W37" s="5" t="n"/>
       <c r="X37" s="5" t="n"/>
     </row>
-    <row r="38" ht="43.5" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>포장 이음부의 충분한 전압과 평탄성의 적정여 부?</t>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>완성된 포장의 두께 및 평탄성과 유지관리 상태의 적정여부?</t>
         </is>
       </c>
       <c r="D38" s="5" t="n"/>
@@ -1451,29 +1509,29 @@
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="5" t="n"/>
       <c r="L38" s="5" t="n"/>
-      <c r="M38" s="9" t="inlineStr"/>
+      <c r="M38" s="10" t="n"/>
       <c r="N38" s="5" t="n"/>
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="9" t="inlineStr"/>
+      <c r="Q38" s="10" t="n"/>
       <c r="R38" s="5" t="n"/>
-      <c r="S38" s="9" t="inlineStr"/>
+      <c r="S38" s="10" t="n"/>
       <c r="T38" s="5" t="n"/>
-      <c r="U38" s="9" t="inlineStr"/>
+      <c r="U38" s="10" t="n"/>
       <c r="V38" s="5" t="n"/>
       <c r="W38" s="5" t="n"/>
       <c r="X38" s="5" t="n"/>
     </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>로울러 속도를 5km/hr 이내로하고 뒷바퀴폭이 1/2로 중복다짐하고 있는지 여부?</t>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>각종 시험관리의 이행 및 결과 보존여부?</t>
         </is>
       </c>
       <c r="D39" s="5" t="n"/>
@@ -1485,29 +1543,29 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5" t="n"/>
       <c r="L39" s="5" t="n"/>
-      <c r="M39" s="9" t="inlineStr"/>
+      <c r="M39" s="10" t="n"/>
       <c r="N39" s="5" t="n"/>
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="9" t="inlineStr"/>
+      <c r="Q39" s="10" t="n"/>
       <c r="R39" s="5" t="n"/>
-      <c r="S39" s="9" t="inlineStr"/>
+      <c r="S39" s="10" t="n"/>
       <c r="T39" s="5" t="n"/>
-      <c r="U39" s="9" t="inlineStr"/>
+      <c r="U39" s="10" t="n"/>
       <c r="V39" s="5" t="n"/>
       <c r="W39" s="5" t="n"/>
       <c r="X39" s="5" t="n"/>
     </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="B40" s="5" t="n"/>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>포장다짐후 포장이 충분히식어 굳어질때까지 교통통제를 적절히 시행하고 있는지 여부?</t>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>포장 이음부의 충분한 전압과 평탄성의 적정여 부?</t>
         </is>
       </c>
       <c r="D40" s="5" t="n"/>
@@ -1519,108 +1577,229 @@
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="5" t="n"/>
       <c r="L40" s="5" t="n"/>
-      <c r="M40" s="9" t="inlineStr"/>
+      <c r="M40" s="10" t="n"/>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="9" t="inlineStr"/>
+      <c r="Q40" s="10" t="n"/>
       <c r="R40" s="5" t="n"/>
-      <c r="S40" s="9" t="inlineStr"/>
+      <c r="S40" s="10" t="n"/>
       <c r="T40" s="5" t="n"/>
-      <c r="U40" s="9" t="inlineStr"/>
+      <c r="U40" s="10" t="n"/>
       <c r="V40" s="5" t="n"/>
       <c r="W40" s="5" t="n"/>
       <c r="X40" s="5" t="n"/>
     </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="10" customHeight="1"/>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="K44" s="11" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>로울러 속도를 5km/hr 이내로하고 뒷바퀴폭이 1/2로 중복다짐하고 있는지 여부?</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="5" t="n"/>
+      <c r="W41" s="5" t="n"/>
+      <c r="X41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>포장다짐후 포장이 충분히식어 굳어질때까지 교통통제를 적절히 시행하고 있는지 여부?</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="5" t="n"/>
+      <c r="W42" s="5" t="n"/>
+      <c r="X42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="13">
+        <f>IF(COUNTA(Q33:Q42,S33:S42)=0,"","합격 "&amp;COUNTA(Q33:Q42)&amp;" · 불합격 "&amp;COUNTA(S33:S42))</f>
+        <v/>
+      </c>
+      <c r="V43" s="5" t="n"/>
+      <c r="W43" s="5" t="n"/>
+      <c r="X43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="15" t="inlineStr"/>
+      <c r="K47" s="16" t="inlineStr">
         <is>
           <t>시공자 점검직원</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="Q47" s="17" t="n"/>
+      <c r="U47" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="K45" s="11" t="inlineStr">
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="15" t="inlineStr"/>
+      <c r="K48" s="16" t="inlineStr">
         <is>
           <t>검측 감리원</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="Q48" s="17" t="n"/>
+      <c r="U48" s="18" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>합격 칸·불합격 칸을 누르면 목록(A · UA)이 나옵니다. 표마다 맨 아래에 합격·불합격 개수가 저절로 셉니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="155">
+  <mergeCells count="167">
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="U39:X39"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="M14:P14"/>
     <mergeCell ref="U38:X38"/>
-    <mergeCell ref="K45:R45"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="U40:X40"/>
-    <mergeCell ref="S45:X45"/>
+    <mergeCell ref="K48:P48"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="U15:X15"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="K44:R44"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C42:L42"/>
     <mergeCell ref="Q35:R35"/>
     <mergeCell ref="S19:T19"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="Q27:R27"/>
     <mergeCell ref="U16:X16"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="U25:X25"/>
-    <mergeCell ref="Q30:R30"/>
     <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S30:T30"/>
     <mergeCell ref="Q17:R17"/>
     <mergeCell ref="M16:P16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="S20:T20"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="A28:T28"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="M18:P18"/>
+    <mergeCell ref="U28:X28"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="C39:L39"/>
     <mergeCell ref="M17:P17"/>
@@ -1633,15 +1812,11 @@
     <mergeCell ref="M19:P19"/>
     <mergeCell ref="S39:T39"/>
     <mergeCell ref="C13:L13"/>
-    <mergeCell ref="A50:X50"/>
     <mergeCell ref="Q38:R38"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="S38:T38"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="S13:T13"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="Q31:R31"/>
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="Q40:R40"/>
@@ -1650,61 +1825,73 @@
     <mergeCell ref="S15:T15"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="A28:X28"/>
-    <mergeCell ref="S24:T24"/>
     <mergeCell ref="C35:L35"/>
-    <mergeCell ref="S44:X44"/>
+    <mergeCell ref="U48:X48"/>
     <mergeCell ref="S33:T33"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="C16:L16"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="A30:X30"/>
     <mergeCell ref="M13:P13"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="U43:X43"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="U18:X18"/>
     <mergeCell ref="U33:X33"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="A54:X54"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="S42:T42"/>
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="U19:X19"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="M34:P34"/>
     <mergeCell ref="S14:T14"/>
-    <mergeCell ref="M34:P34"/>
     <mergeCell ref="S37:T37"/>
     <mergeCell ref="C14:L14"/>
     <mergeCell ref="U36:X36"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="A53:X53"/>
+    <mergeCell ref="A21:T21"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C41:L41"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="M31:P31"/>
     <mergeCell ref="U37:X37"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="U13:X13"/>
     <mergeCell ref="Q32:R32"/>
     <mergeCell ref="A11:X11"/>
+    <mergeCell ref="U21:X21"/>
     <mergeCell ref="S32:T32"/>
+    <mergeCell ref="Q41:R41"/>
     <mergeCell ref="S26:T26"/>
     <mergeCell ref="A40:B40"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="A43:T43"/>
+    <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K47:P47"/>
     <mergeCell ref="S16:T16"/>
     <mergeCell ref="Q25:R25"/>
     <mergeCell ref="S25:T25"/>
     <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q48:T48"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q33:R33"/>
     <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S27:T27"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="A46:X46"/>
     <mergeCell ref="C19:L19"/>
@@ -1713,32 +1900,1506 @@
     <mergeCell ref="U26:X26"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="U35:X35"/>
+    <mergeCell ref="Q47:T47"/>
     <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A48:J48"/>
     <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A23:X23"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="U34:X34"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="Q34:R34"/>
     <mergeCell ref="S34:T34"/>
-    <mergeCell ref="A43:X43"/>
-    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="A52:X52"/>
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="M20:P20"/>
     <mergeCell ref="Q36:R36"/>
     <mergeCell ref="S36:T36"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C31:L31"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="M30:P30"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A49:X49"/>
     <mergeCell ref="M1:X1"/>
     <mergeCell ref="M15:P15"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M37:P37"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <dataValidations count="2">
+    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q26 Q27 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S26 S27 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"UA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>검 측 체 크 리 스 트  (포장공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공        종</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>포장공 — 아스팔트 표층</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  위치 및 부위</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>STA.0+000 ~ 0+300</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 일 자</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공  사  량</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>A=1,800㎡</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>▣ 보조기층,기층</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>재료의 입도분포 및 유해물 포함여부?</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>다짐층의 두께(20cm) 및 전압밀도(95%) 적정 여부?</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>포설시 최적함수비 유지 및 입도분리 방지대책 강구 여부?</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>구조물 주위의 다짐 및 보호상태 여부?</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>사면의 구배 및 배수로 상태의 적정여부?</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>규정된 성형,단면,표고,구배의 적정여부?</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>보조기층 시공전 노면상의 스폰지,먼지, 점토, 기타 불순물을 깨끗이 정리여부?</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="10" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="13">
+        <f>IF(COUNTA(Q14:Q20,S14:S20)=0,"","합격 "&amp;COUNTA(Q14:Q20)&amp;" · 불합격 "&amp;COUNTA(S14:S20))</f>
+        <v/>
+      </c>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>▣ 보조기층, 기층</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="6" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>각종 관리시험의 이행 및 결과의 보존 여부?</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>두께는 시방서에 규정된 허용 범위내에 드는지 여부?</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="10" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="5" t="n"/>
+      <c r="U28" s="13">
+        <f>IF(COUNTA(Q26:Q27,S26:S27)=0,"","합격 "&amp;COUNTA(Q26:Q27)&amp;" · 불합격 "&amp;COUNTA(S26:S27))</f>
+        <v/>
+      </c>
+      <c r="V28" s="5" t="n"/>
+      <c r="W28" s="5" t="n"/>
+      <c r="X28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>▣ 아스팔트 포장</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>검사 항목</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>검사기준</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="9" t="inlineStr">
+        <is>
+          <t>합격</t>
+        </is>
+      </c>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>불합격</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>조치사항</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>기층표면 청소상태의 적정여부?</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="10" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>프라임 텍코트용 역청재의 사용량,살포온도,양생기간의 적정여부?</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>골재 가열온도,혼합물, 생산 및 현장도착시의 온도관리?</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>포설중 혼합물의 재료분리 여부?</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="5" t="n"/>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>포장 장비의 조합, 전압순서 및 회수등의 시공계획 수립여부?</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>완성된 포장의 두께 및 평탄성과 유지관리 상태의 적정여부?</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="5" t="n"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
+      <c r="X38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>각종 시험관리의 이행 및 결과 보존여부?</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="5" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="5" t="n"/>
+      <c r="W39" s="5" t="n"/>
+      <c r="X39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>포장 이음부의 충분한 전압과 평탄성의 적정여 부?</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="5" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="5" t="n"/>
+      <c r="W40" s="5" t="n"/>
+      <c r="X40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>로울러 속도를 5km/hr 이내로하고 뒷바퀴폭이 1/2로 중복다짐하고 있는지 여부?</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n"/>
+      <c r="S41" s="10" t="n"/>
+      <c r="T41" s="5" t="n"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="5" t="n"/>
+      <c r="W41" s="5" t="n"/>
+      <c r="X41" s="5" t="n"/>
+    </row>
+    <row r="42" ht="45" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>포장다짐후 포장이 충분히식어 굳어질때까지 교통통제를 적절히 시행하고 있는지 여부?</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="5" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="5" t="n"/>
+      <c r="W42" s="5" t="n"/>
+      <c r="X42" s="5" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>결  과</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="13">
+        <f>IF(COUNTA(Q33:Q42,S33:S42)=0,"","합격 "&amp;COUNTA(Q33:Q42)&amp;" · 불합격 "&amp;COUNTA(S33:S42))</f>
+        <v/>
+      </c>
+      <c r="V43" s="5" t="n"/>
+      <c r="W43" s="5" t="n"/>
+      <c r="X43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="10" customHeight="1"/>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="15" t="inlineStr"/>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>시공자 점검직원</t>
+        </is>
+      </c>
+      <c r="Q47" s="17" t="inlineStr">
+        <is>
+          <t>이감독</t>
+        </is>
+      </c>
+      <c r="U47" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="15" t="inlineStr"/>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>검측 감리원</t>
+        </is>
+      </c>
+      <c r="Q48" s="17" t="inlineStr">
+        <is>
+          <t>박감리</t>
+        </is>
+      </c>
+      <c r="U48" s="18" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="165">
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="U40:X40"/>
+    <mergeCell ref="K48:P48"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="A28:T28"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="U42:X42"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="A30:X30"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="U43:X43"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="S42:T42"/>
+    <mergeCell ref="C37:L37"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="S37:T37"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="A11:X11"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="A43:T43"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="K47:P47"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="Q48:T48"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="A46:X46"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="Q47:T47"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A23:X23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="A52:X52"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A49:X49"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="M15:P15"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q26 Q27 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S26 S27 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
+      <formula1>"UA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/geomcheuk-pojang.xlsx
+++ b/web/public/forms/geomcheuk-pojang.xlsx
@@ -601,7 +601,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="21" t="inlineStr">

--- a/web/public/forms/geomcheuk-pojang.xlsx
+++ b/web/public/forms/geomcheuk-pojang.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="포장공 검측 체크리스트" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'포장공 검측 체크리스트'!$A$1:$X$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -200,9 +198,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1091,10 +1086,7 @@
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
-      <c r="U21" s="13">
-        <f>IF(COUNTA(Q14:Q20,S14:S20)=0,"","합격 "&amp;COUNTA(Q14:Q20)&amp;" · 불합격 "&amp;COUNTA(S14:S20))</f>
-        <v/>
-      </c>
+      <c r="U21" s="13" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
@@ -1251,10 +1243,7 @@
       <c r="R28" s="5" t="n"/>
       <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
-      <c r="U28" s="13">
-        <f>IF(COUNTA(Q26:Q27,S26:S27)=0,"","합격 "&amp;COUNTA(Q26:Q27)&amp;" · 불합격 "&amp;COUNTA(S26:S27))</f>
-        <v/>
-      </c>
+      <c r="U28" s="13" t="n"/>
       <c r="V28" s="5" t="n"/>
       <c r="W28" s="5" t="n"/>
       <c r="X28" s="5" t="n"/>
@@ -1683,10 +1672,7 @@
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5" t="n"/>
       <c r="T43" s="5" t="n"/>
-      <c r="U43" s="13">
-        <f>IF(COUNTA(Q33:Q42,S33:S42)=0,"","합격 "&amp;COUNTA(Q33:Q42)&amp;" · 불합격 "&amp;COUNTA(S33:S42))</f>
-        <v/>
-      </c>
+      <c r="U43" s="13" t="n"/>
       <c r="V43" s="5" t="n"/>
       <c r="W43" s="5" t="n"/>
       <c r="X43" s="5" t="n"/>
@@ -1736,6 +1722,7 @@
       </c>
     </row>
     <row r="50" ht="6" customHeight="1"/>
+    <row r="51"/>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="20" t="inlineStr">
         <is>
@@ -1939,1467 +1926,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>검 측 체 크 리 스 트  (포장공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공        종</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>포장공 — 아스팔트 표층</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  위치 및 부위</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>STA.0+000 ~ 0+300</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 일 자</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공  사  량</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>A=1,800㎡</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>▣ 보조기층,기층</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>재료의 입도분포 및 유해물 포함여부?</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="10" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="10" t="n"/>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>다짐층의 두께(20cm) 및 전압밀도(95%) 적정 여부?</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="10" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="10" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>포설시 최적함수비 유지 및 입도분리 방지대책 강구 여부?</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="10" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="10" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="10" t="n"/>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>구조물 주위의 다짐 및 보호상태 여부?</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="10" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="10" t="n"/>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>사면의 구배 및 배수로 상태의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="10" t="n"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>규정된 성형,단면,표고,구배의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>보조기층 시공전 노면상의 스폰지,먼지, 점토, 기타 불순물을 깨끗이 정리여부?</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="10" t="n"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="13">
-        <f>IF(COUNTA(Q14:Q20,S14:S20)=0,"","합격 "&amp;COUNTA(Q14:Q20)&amp;" · 불합격 "&amp;COUNTA(S14:S20))</f>
-        <v/>
-      </c>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>▣ 보조기층, 기층</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>각종 관리시험의 이행 및 결과의 보존 여부?</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="10" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="10" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="10" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>두께는 시방서에 규정된 허용 범위내에 드는지 여부?</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="10" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="10" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="n"/>
-      <c r="P28" s="5" t="n"/>
-      <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="n"/>
-      <c r="U28" s="13">
-        <f>IF(COUNTA(Q26:Q27,S26:S27)=0,"","합격 "&amp;COUNTA(Q26:Q27)&amp;" · 불합격 "&amp;COUNTA(S26:S27))</f>
-        <v/>
-      </c>
-      <c r="V28" s="5" t="n"/>
-      <c r="W28" s="5" t="n"/>
-      <c r="X28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>▣ 아스팔트 포장</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="6" customHeight="1"/>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>검사 항목</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>검사기준</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="9" t="inlineStr">
-        <is>
-          <t>조치사항</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>기층표면 청소상태의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="10" t="n"/>
-      <c r="N33" s="5" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="10" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>프라임 텍코트용 역청재의 사용량,살포온도,양생기간의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="10" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="10" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>골재 가열온도,혼합물, 생산 및 현장도착시의 온도관리?</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="10" t="n"/>
-      <c r="N35" s="5" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="10" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>포설중 혼합물의 재료분리 여부?</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="10" t="n"/>
-      <c r="N36" s="5" t="n"/>
-      <c r="O36" s="5" t="n"/>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="10" t="n"/>
-      <c r="T36" s="5" t="n"/>
-      <c r="U36" s="10" t="n"/>
-      <c r="V36" s="5" t="n"/>
-      <c r="W36" s="5" t="n"/>
-      <c r="X36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>포장 장비의 조합, 전압순서 및 회수등의 시공계획 수립여부?</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="10" t="n"/>
-      <c r="N37" s="5" t="n"/>
-      <c r="O37" s="5" t="n"/>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R37" s="5" t="n"/>
-      <c r="S37" s="10" t="n"/>
-      <c r="T37" s="5" t="n"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="5" t="n"/>
-      <c r="W37" s="5" t="n"/>
-      <c r="X37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>완성된 포장의 두께 및 평탄성과 유지관리 상태의 적정여부?</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="n"/>
-      <c r="M38" s="10" t="n"/>
-      <c r="N38" s="5" t="n"/>
-      <c r="O38" s="5" t="n"/>
-      <c r="P38" s="5" t="n"/>
-      <c r="Q38" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R38" s="5" t="n"/>
-      <c r="S38" s="10" t="n"/>
-      <c r="T38" s="5" t="n"/>
-      <c r="U38" s="10" t="n"/>
-      <c r="V38" s="5" t="n"/>
-      <c r="W38" s="5" t="n"/>
-      <c r="X38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>각종 시험관리의 이행 및 결과 보존여부?</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="n"/>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="5" t="n"/>
-      <c r="O39" s="5" t="n"/>
-      <c r="P39" s="5" t="n"/>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R39" s="5" t="n"/>
-      <c r="S39" s="10" t="n"/>
-      <c r="T39" s="5" t="n"/>
-      <c r="U39" s="10" t="n"/>
-      <c r="V39" s="5" t="n"/>
-      <c r="W39" s="5" t="n"/>
-      <c r="X39" s="5" t="n"/>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>포장 이음부의 충분한 전압과 평탄성의 적정여 부?</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="5" t="n"/>
-      <c r="P40" s="5" t="n"/>
-      <c r="Q40" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="5" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="5" t="n"/>
-      <c r="W40" s="5" t="n"/>
-      <c r="X40" s="5" t="n"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>로울러 속도를 5km/hr 이내로하고 뒷바퀴폭이 1/2로 중복다짐하고 있는지 여부?</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="5" t="n"/>
-      <c r="Q41" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R41" s="5" t="n"/>
-      <c r="S41" s="10" t="n"/>
-      <c r="T41" s="5" t="n"/>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="5" t="n"/>
-      <c r="W41" s="5" t="n"/>
-      <c r="X41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>포장다짐후 포장이 충분히식어 굳어질때까지 교통통제를 적절히 시행하고 있는지 여부?</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="5" t="n"/>
-      <c r="Q42" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="5" t="n"/>
-      <c r="U42" s="10" t="n"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>결  과</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="5" t="n"/>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
-      <c r="S43" s="5" t="n"/>
-      <c r="T43" s="5" t="n"/>
-      <c r="U43" s="13">
-        <f>IF(COUNTA(Q33:Q42,S33:S42)=0,"","합격 "&amp;COUNTA(Q33:Q42)&amp;" · 불합격 "&amp;COUNTA(S33:S42))</f>
-        <v/>
-      </c>
-      <c r="V43" s="5" t="n"/>
-      <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="10" customHeight="1"/>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="14" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="15" t="inlineStr"/>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>시공자 점검직원</t>
-        </is>
-      </c>
-      <c r="Q47" s="17" t="inlineStr">
-        <is>
-          <t>이감독</t>
-        </is>
-      </c>
-      <c r="U47" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="15" t="inlineStr"/>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t>검측 감리원</t>
-        </is>
-      </c>
-      <c r="Q48" s="17" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="U48" s="18" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>※ 검사·시험값이 있으면 값을 적고, 합격은 A · 불합격은 UA 로 표기합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="165">
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="U39:X39"/>
-    <mergeCell ref="M32:P32"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="U38:X38"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="U40:X40"/>
-    <mergeCell ref="K48:P48"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="A28:T28"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="M33:P33"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="U42:X42"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="C38:L38"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="U48:X48"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="U41:X41"/>
-    <mergeCell ref="A30:X30"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="U47:X47"/>
-    <mergeCell ref="U43:X43"/>
-    <mergeCell ref="C36:L36"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M27:P27"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="M36:P36"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="S42:T42"/>
-    <mergeCell ref="C37:L37"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="S37:T37"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="A21:T21"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="A11:X11"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="A43:T43"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="K47:P47"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="Q48:T48"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="M38:P38"/>
-    <mergeCell ref="A46:X46"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="Q47:T47"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A48:J48"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A23:X23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="A52:X52"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A49:X49"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="M15:P15"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q26 Q27 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"A"</formula1>
-    </dataValidation>
-    <dataValidation sqref="S14 S15 S16 S17 S18 S19 S20 S26 S27 S33 S34 S35 S36 S37 S38 S39 S40 S41 S42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"UA"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/geomcheuk-pojang.xlsx
+++ b/web/public/forms/geomcheuk-pojang.xlsx
@@ -596,7 +596,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
